--- a/SGC-CKN/Excel/cd71e2d8-2b59-4ed9-abb5-dbbeb729a20d_CT-02_PT-47_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/cd71e2d8-2b59-4ed9-abb5-dbbeb729a20d_CT-02_PT-47_D800_19-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>PT-47</t>
+    <t>P7-47</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -147,7 +147,7 @@
 19/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">18:51
+    <t xml:space="preserve">18:31
 19/03/2026</t>
   </si>
   <si>
@@ -157,7 +157,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">18:52
+    <t xml:space="preserve">18:32
 19/03/2026</t>
   </si>
   <si>
@@ -175,56 +175,50 @@
 19/03/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">20:25
+19/03/2026</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:26
+19/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:58
+19/03/2026</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:59
+19/03/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">21:25
 19/03/2026</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">21:26
 19/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">21:58
-19/03/2026</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:59
-19/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:25
-19/03/2026</t>
-  </si>
-  <si>
-    <t>Thời gian kết thúc viết nhầm là 21h25, hiệu chỉnh thành 22h25 để đảm bảo tính liên tục.</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:26
-19/03/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">22:38
 19/03/2026</t>
-  </si>
-  <si>
-    <t>Thời gian bắt đầu viết nhầm là 21h26, hiệu chỉnh thành 22h26.</t>
   </si>
   <si>
     <t>10</t>
@@ -427,12 +421,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFFED7AA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFED7AA"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -614,17 +608,17 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1245,7 +1239,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.42</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.19</v>
@@ -1254,10 +1248,10 @@
         <v>0.22</v>
       </c>
       <c r="I11" s="5">
-        <v>3.77</v>
+        <v>7.19</v>
       </c>
       <c r="J11" s="8">
-        <v>17.4</v>
+        <v>33.18</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1356,13 +1350,13 @@
         <v>-21.88</v>
       </c>
       <c r="H14" s="15">
-        <v>0.77</v>
+        <v>0.43</v>
       </c>
       <c r="I14" s="15">
         <v>4.35</v>
       </c>
       <c r="J14" s="8">
-        <v>5.67</v>
+        <v>10.04</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1391,13 +1385,13 @@
         <v>-25.98</v>
       </c>
       <c r="H15" s="18">
-        <v>0.13</v>
+        <v>0.47</v>
       </c>
       <c r="I15" s="18">
         <v>4.1</v>
       </c>
       <c r="J15" s="8">
-        <v>30.75</v>
+        <v>8.79</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1426,50 +1420,50 @@
         <v>-36.18</v>
       </c>
       <c r="H16" s="21">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="I16" s="21">
         <v>10.2</v>
       </c>
-      <c r="J16" s="24">
-        <v>4.37</v>
+      <c r="J16" s="8">
+        <v>7.65</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>-36.18</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>-38.53</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>0.53</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>2.35</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J17" s="27">
         <v>4.41</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="25" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1501,28 +1495,28 @@
       <c r="I18" s="28">
         <v>1.57</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="27">
         <v>3.62</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>62</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>63</v>
       </c>
       <c r="F19" s="31">
         <v>-40.1</v>
@@ -1531,33 +1525,33 @@
         <v>-44.2</v>
       </c>
       <c r="H19" s="31">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="I19" s="31">
         <v>4.1</v>
       </c>
-      <c r="J19" s="8">
-        <v>20.5</v>
+      <c r="J19" s="27">
+        <v>3.42</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>66</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>68</v>
       </c>
       <c r="F20" s="34">
         <v>-44.2</v>
@@ -1580,7 +1574,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1686,31 +1680,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1727,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.42</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.19</v>
@@ -1736,10 +1730,10 @@
         <v>0.22</v>
       </c>
       <c r="H2" s="5">
-        <v>3.77</v>
+        <v>7.19</v>
       </c>
       <c r="I2" s="8">
-        <v>17.4</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1820,13 +1814,13 @@
         <v>-21.88</v>
       </c>
       <c r="G5" s="15">
-        <v>0.77</v>
+        <v>0.43</v>
       </c>
       <c r="H5" s="15">
         <v>4.35</v>
       </c>
       <c r="I5" s="8">
-        <v>5.67</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1849,13 +1843,13 @@
         <v>-25.98</v>
       </c>
       <c r="G6" s="18">
-        <v>0.13</v>
+        <v>0.47</v>
       </c>
       <c r="H6" s="18">
         <v>4.1</v>
       </c>
       <c r="I6" s="8">
-        <v>30.75</v>
+        <v>8.79</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1878,41 +1872,41 @@
         <v>-36.18</v>
       </c>
       <c r="G7" s="21">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="H7" s="21">
         <v>10.2</v>
       </c>
-      <c r="I7" s="24">
-        <v>4.37</v>
+      <c r="I7" s="8">
+        <v>7.65</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <v>-36.18</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <v>-38.53</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <v>0.53</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
         <v>2.35</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="27">
         <v>4.41</v>
       </c>
     </row>
@@ -1941,7 +1935,7 @@
       <c r="H9" s="28">
         <v>1.57</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="27">
         <v>3.62</v>
       </c>
     </row>
@@ -1953,7 +1947,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1965,13 +1959,13 @@
         <v>-44.2</v>
       </c>
       <c r="G10" s="31">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="H10" s="31">
         <v>4.1</v>
       </c>
-      <c r="I10" s="8">
-        <v>20.5</v>
+      <c r="I10" s="27">
+        <v>3.42</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1982,7 +1976,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -2005,7 +1999,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -2017,7 +2011,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.42</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-49.8</v>
@@ -2026,10 +2020,10 @@
         <v>5.47</v>
       </c>
       <c r="H12" s="39">
-        <v>46.38</v>
+        <v>49.8</v>
       </c>
       <c r="I12" s="39">
-        <v>8.48</v>
+        <v>9.11</v>
       </c>
     </row>
   </sheetData>
